--- a/test summary.xlsx
+++ b/test summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vansh\projects\phisguard-nobackend\testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vansh\projects\ClueWell-Mail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC945355-3B7E-4132-BD4C-FBB4277E6E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEBAB14-AAD3-42DD-931D-F0198148B2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="14016" windowHeight="12336" xr2:uid="{B026CC31-BFE6-4175-9DC2-82E30F74CC32}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B026CC31-BFE6-4175-9DC2-82E30F74CC32}"/>
   </bookViews>
   <sheets>
     <sheet name="test summary" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="59">
   <si>
     <t>TEST-ID</t>
   </si>
@@ -297,6 +297,28 @@
 https://library.university-example.edu/hours/examination-week
 Regards,
 University Library</t>
+  </si>
+  <si>
+    <t>Exclusive Member Reward: Your ₹7,500 Shopping Voucher Expires Tonight</t>
+  </si>
+  <si>
+    <t>Dear Valued Customer,
+Thank you for being a loyal member of our shopping rewards program.
+As part of our latest customer appreciation campaign, your account has been selected for a ₹7,500 promotional shopping voucher. This voucher can be used on eligible electronics, home appliances, and lifestyle products during our ongoing seasonal sale.
+Your exclusive benefits include:
+- ₹7,500 promotional shopping voucher.
+- Additional discounts on selected products.
+- Complimentary delivery on qualifying orders.
+- Early access to limited-stock offers.
+Important: The promotional voucher is available until 11:59 PM today. Unused promotional benefits will expire automatically after the campaign period.
+To review your available rewards and applicable terms, please visit the shopping rewards section of your customer account.
+Thank you for shopping with us.
+Customer Rewards Department
+Retail Promotions &amp; Member Benefits
+ChatGPT can make mistakes. Check important info.</t>
+  </si>
+  <si>
+    <t>offers@retailbenefits.com</t>
   </si>
 </sst>
 </file>
@@ -449,54 +471,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -517,16 +530,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -534,6 +537,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -559,13 +571,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -574,6 +579,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1065,2426 +1077,2441 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
-    <col min="2" max="2" width="43" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.88671875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="43" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="77" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.109375" customWidth="1"/>
     <col min="6" max="6" width="12.5546875" customWidth="1"/>
     <col min="7" max="7" width="13.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" style="26" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" customWidth="1"/>
     <col min="9" max="9" width="9.6640625" customWidth="1"/>
     <col min="10" max="11" width="4.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="6"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="str">
+      <c r="A3" s="18" t="str">
         <f>"Test "&amp;TEXT(ROW()-2,"000")</f>
         <v>Test 001</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="13">
         <v>0.97</v>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="14">
         <v>0.99</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="144" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="str">
+      <c r="A4" s="18" t="str">
         <f t="shared" ref="A4:A67" si="0">"Test "&amp;TEXT(ROW()-2,"000")</f>
         <v>Test 002</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="13">
         <v>0.95</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="20">
         <v>0.94</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="str">
+      <c r="A5" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 003</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="13">
         <v>0.08</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="20">
         <v>0.84</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="str">
+      <c r="A6" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 004</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="13">
         <v>0.08</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="20">
         <v>0.84</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="216" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="str">
+      <c r="A7" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 005</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="13">
         <v>0.97</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="20">
         <v>0.99</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="str">
+      <c r="A8" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 006</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="13">
         <v>0.08</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="20">
         <v>0.84</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I8" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="str">
+      <c r="A9" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 007</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="13">
         <v>0.97</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="20">
         <v>0.97</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="str">
+      <c r="A10" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 008</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="13">
         <v>0.97</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="20">
         <v>0.91</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="str">
+      <c r="A11" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 009</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="13">
         <v>0.63</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="20">
         <v>0.87</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="15" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="str">
+      <c r="A12" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 010</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="13">
         <v>0.8</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="20">
         <v>0.89</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="str">
+      <c r="A13" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 011</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="13">
         <v>0.08</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="20">
         <v>0.84</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="21" t="str">
+      <c r="A14" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 012</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="13">
         <v>0.59</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="20">
         <v>0.86</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="I14" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="str">
+      <c r="A15" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 013</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="13">
         <v>0.97</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="20">
         <v>0.99</v>
       </c>
-      <c r="I15" s="18" t="s">
+      <c r="I15" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="21" t="str">
+      <c r="A16" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 014</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="13">
         <v>0.08</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="20">
         <v>0.84</v>
       </c>
-      <c r="I16" s="18" t="s">
+      <c r="I16" s="15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="str">
+    <row r="17" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 015</v>
       </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="18"/>
+      <c r="B17" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="13">
+        <v>0.12</v>
+      </c>
+      <c r="H17" s="20">
+        <v>0.89</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="18" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="str">
+      <c r="A18" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 016</v>
       </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="18"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="15"/>
     </row>
     <row r="19" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="str">
+      <c r="A19" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 017</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="18"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="15"/>
     </row>
     <row r="20" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A20" s="21" t="str">
+      <c r="A20" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 018</v>
       </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="18"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="15"/>
     </row>
     <row r="21" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A21" s="21" t="str">
+      <c r="A21" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 019</v>
       </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="18"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="15"/>
     </row>
     <row r="22" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A22" s="21" t="str">
+      <c r="A22" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 020</v>
       </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="18"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="15"/>
     </row>
     <row r="23" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A23" s="21" t="str">
+      <c r="A23" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 021</v>
       </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="18"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="15"/>
     </row>
     <row r="24" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A24" s="21" t="str">
+      <c r="A24" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 022</v>
       </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="18"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="15"/>
     </row>
     <row r="25" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A25" s="21" t="str">
+      <c r="A25" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 023</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="18"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="15"/>
     </row>
     <row r="26" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A26" s="21" t="str">
+      <c r="A26" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 024</v>
       </c>
-      <c r="B26" s="23"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="18"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="15"/>
     </row>
     <row r="27" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="str">
+      <c r="A27" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 025</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="18"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="15"/>
     </row>
     <row r="28" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A28" s="21" t="str">
+      <c r="A28" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 026</v>
       </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="18"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="15"/>
     </row>
     <row r="29" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A29" s="21" t="str">
+      <c r="A29" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 027</v>
       </c>
-      <c r="B29" s="23"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="18"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="15"/>
     </row>
     <row r="30" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A30" s="21" t="str">
+      <c r="A30" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 028</v>
       </c>
-      <c r="B30" s="23"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="18"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="15"/>
     </row>
     <row r="31" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="str">
+      <c r="A31" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 029</v>
       </c>
-      <c r="B31" s="23"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="18"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="15"/>
     </row>
     <row r="32" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A32" s="21" t="str">
+      <c r="A32" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 030</v>
       </c>
-      <c r="B32" s="23"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="18"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="15"/>
     </row>
     <row r="33" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A33" s="21" t="str">
+      <c r="A33" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 031</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="18"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="15"/>
     </row>
     <row r="34" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A34" s="21" t="str">
+      <c r="A34" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 032</v>
       </c>
-      <c r="B34" s="23"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="18"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="15"/>
     </row>
     <row r="35" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A35" s="21" t="str">
+      <c r="A35" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 033</v>
       </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="18"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="15"/>
     </row>
     <row r="36" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A36" s="21" t="str">
+      <c r="A36" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 034</v>
       </c>
-      <c r="B36" s="23"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="18"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="15"/>
     </row>
     <row r="37" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A37" s="21" t="str">
+      <c r="A37" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 035</v>
       </c>
-      <c r="B37" s="23"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="18"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="15"/>
     </row>
     <row r="38" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A38" s="21" t="str">
+      <c r="A38" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 036</v>
       </c>
-      <c r="B38" s="23"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="18"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="15"/>
     </row>
     <row r="39" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A39" s="21" t="str">
+      <c r="A39" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 037</v>
       </c>
-      <c r="B39" s="23"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="18"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="15"/>
     </row>
     <row r="40" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A40" s="21" t="str">
+      <c r="A40" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 038</v>
       </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="18"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="15"/>
     </row>
     <row r="41" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A41" s="21" t="str">
+      <c r="A41" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 039</v>
       </c>
-      <c r="B41" s="23"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="18"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="15"/>
     </row>
     <row r="42" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A42" s="21" t="str">
+      <c r="A42" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 040</v>
       </c>
-      <c r="B42" s="23"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="18"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="15"/>
     </row>
     <row r="43" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A43" s="21" t="str">
+      <c r="A43" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 041</v>
       </c>
-      <c r="B43" s="23"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="18"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="15"/>
     </row>
     <row r="44" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A44" s="21" t="str">
+      <c r="A44" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 042</v>
       </c>
-      <c r="B44" s="23"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="18"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="15"/>
     </row>
     <row r="45" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A45" s="21" t="str">
+      <c r="A45" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 043</v>
       </c>
-      <c r="B45" s="23"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="18"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="15"/>
     </row>
     <row r="46" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A46" s="21" t="str">
+      <c r="A46" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 044</v>
       </c>
-      <c r="B46" s="23"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="18"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="15"/>
     </row>
     <row r="47" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A47" s="21" t="str">
+      <c r="A47" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 045</v>
       </c>
-      <c r="B47" s="23"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="18"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="21"/>
+      <c r="I47" s="15"/>
     </row>
     <row r="48" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A48" s="21" t="str">
+      <c r="A48" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 046</v>
       </c>
-      <c r="B48" s="23"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="18"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="21"/>
+      <c r="I48" s="15"/>
     </row>
     <row r="49" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A49" s="21" t="str">
+      <c r="A49" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 047</v>
       </c>
-      <c r="B49" s="23"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="18"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="15"/>
     </row>
     <row r="50" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A50" s="21" t="str">
+      <c r="A50" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 048</v>
       </c>
-      <c r="B50" s="23"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="28"/>
-      <c r="I50" s="18"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="21"/>
+      <c r="I50" s="15"/>
     </row>
     <row r="51" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A51" s="21" t="str">
+      <c r="A51" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 049</v>
       </c>
-      <c r="B51" s="23"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="18"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="15"/>
     </row>
     <row r="52" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A52" s="21" t="str">
+      <c r="A52" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 050</v>
       </c>
-      <c r="B52" s="23"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="18"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="15"/>
     </row>
     <row r="53" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A53" s="21" t="str">
+      <c r="A53" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 051</v>
       </c>
-      <c r="B53" s="23"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="18"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="15"/>
     </row>
     <row r="54" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A54" s="21" t="str">
+      <c r="A54" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 052</v>
       </c>
-      <c r="B54" s="23"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="28"/>
-      <c r="I54" s="18"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="15"/>
     </row>
     <row r="55" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A55" s="21" t="str">
+      <c r="A55" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 053</v>
       </c>
-      <c r="B55" s="23"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="18"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="15"/>
     </row>
     <row r="56" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A56" s="21" t="str">
+      <c r="A56" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 054</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="28"/>
-      <c r="I56" s="18"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="15"/>
     </row>
     <row r="57" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A57" s="21" t="str">
+      <c r="A57" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 055</v>
       </c>
-      <c r="B57" s="23"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="18"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="21"/>
+      <c r="I57" s="15"/>
     </row>
     <row r="58" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A58" s="21" t="str">
+      <c r="A58" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 056</v>
       </c>
-      <c r="B58" s="23"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="18"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="15"/>
     </row>
     <row r="59" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A59" s="21" t="str">
+      <c r="A59" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 057</v>
       </c>
-      <c r="B59" s="23"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="28"/>
-      <c r="I59" s="18"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="21"/>
+      <c r="I59" s="15"/>
     </row>
     <row r="60" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A60" s="21" t="str">
+      <c r="A60" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 058</v>
       </c>
-      <c r="B60" s="23"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="18"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="21"/>
+      <c r="I60" s="15"/>
     </row>
     <row r="61" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A61" s="21" t="str">
+      <c r="A61" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 059</v>
       </c>
-      <c r="B61" s="23"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="18"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="21"/>
+      <c r="I61" s="15"/>
     </row>
     <row r="62" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A62" s="21" t="str">
+      <c r="A62" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 060</v>
       </c>
-      <c r="B62" s="23"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="18"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="15"/>
     </row>
     <row r="63" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A63" s="21" t="str">
+      <c r="A63" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 061</v>
       </c>
-      <c r="B63" s="23"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="28"/>
-      <c r="I63" s="18"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="21"/>
+      <c r="I63" s="15"/>
     </row>
     <row r="64" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A64" s="21" t="str">
+      <c r="A64" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 062</v>
       </c>
-      <c r="B64" s="23"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="18"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="21"/>
+      <c r="I64" s="15"/>
     </row>
     <row r="65" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A65" s="21" t="str">
+      <c r="A65" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 063</v>
       </c>
-      <c r="B65" s="23"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="28"/>
-      <c r="I65" s="18"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="21"/>
+      <c r="I65" s="15"/>
     </row>
     <row r="66" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A66" s="21" t="str">
+      <c r="A66" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 064</v>
       </c>
-      <c r="B66" s="23"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="28"/>
-      <c r="I66" s="18"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="21"/>
+      <c r="I66" s="15"/>
     </row>
     <row r="67" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A67" s="21" t="str">
+      <c r="A67" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Test 065</v>
       </c>
-      <c r="B67" s="23"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="18"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="21"/>
+      <c r="I67" s="15"/>
     </row>
     <row r="68" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A68" s="21" t="str">
+      <c r="A68" s="18" t="str">
         <f t="shared" ref="A68:A131" si="1">"Test "&amp;TEXT(ROW()-2,"000")</f>
         <v>Test 066</v>
       </c>
-      <c r="B68" s="23"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="18"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="15"/>
     </row>
     <row r="69" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A69" s="21" t="str">
+      <c r="A69" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 067</v>
       </c>
-      <c r="B69" s="23"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="15"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="18"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="21"/>
+      <c r="I69" s="15"/>
     </row>
     <row r="70" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A70" s="21" t="str">
+      <c r="A70" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 068</v>
       </c>
-      <c r="B70" s="23"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="15"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="18"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="21"/>
+      <c r="I70" s="15"/>
     </row>
     <row r="71" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A71" s="21" t="str">
+      <c r="A71" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 069</v>
       </c>
-      <c r="B71" s="23"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15"/>
-      <c r="H71" s="28"/>
-      <c r="I71" s="18"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="15"/>
     </row>
     <row r="72" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A72" s="21" t="str">
+      <c r="A72" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 070</v>
       </c>
-      <c r="B72" s="23"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
-      <c r="G72" s="15"/>
-      <c r="H72" s="28"/>
-      <c r="I72" s="18"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="15"/>
     </row>
     <row r="73" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A73" s="21" t="str">
+      <c r="A73" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 071</v>
       </c>
-      <c r="B73" s="23"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="15"/>
-      <c r="G73" s="15"/>
-      <c r="H73" s="28"/>
-      <c r="I73" s="18"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="15"/>
     </row>
     <row r="74" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A74" s="21" t="str">
+      <c r="A74" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 072</v>
       </c>
-      <c r="B74" s="23"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="15"/>
-      <c r="G74" s="15"/>
-      <c r="H74" s="28"/>
-      <c r="I74" s="18"/>
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="15"/>
     </row>
     <row r="75" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A75" s="21" t="str">
+      <c r="A75" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 073</v>
       </c>
-      <c r="B75" s="23"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15"/>
-      <c r="G75" s="15"/>
-      <c r="H75" s="28"/>
-      <c r="I75" s="18"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="21"/>
+      <c r="I75" s="15"/>
     </row>
     <row r="76" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A76" s="21" t="str">
+      <c r="A76" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 074</v>
       </c>
-      <c r="B76" s="23"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="15"/>
-      <c r="G76" s="15"/>
-      <c r="H76" s="28"/>
-      <c r="I76" s="18"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="21"/>
+      <c r="I76" s="15"/>
     </row>
     <row r="77" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A77" s="21" t="str">
+      <c r="A77" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 075</v>
       </c>
-      <c r="B77" s="23"/>
-      <c r="C77" s="12"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="15"/>
-      <c r="H77" s="28"/>
-      <c r="I77" s="18"/>
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="21"/>
+      <c r="I77" s="15"/>
     </row>
     <row r="78" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A78" s="21" t="str">
+      <c r="A78" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 076</v>
       </c>
-      <c r="B78" s="23"/>
-      <c r="C78" s="12"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="15"/>
-      <c r="H78" s="28"/>
-      <c r="I78" s="18"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="21"/>
+      <c r="I78" s="15"/>
     </row>
     <row r="79" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A79" s="21" t="str">
+      <c r="A79" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 077</v>
       </c>
-      <c r="B79" s="23"/>
-      <c r="C79" s="12"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="15"/>
-      <c r="H79" s="28"/>
-      <c r="I79" s="18"/>
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
+      <c r="H79" s="21"/>
+      <c r="I79" s="15"/>
     </row>
     <row r="80" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A80" s="21" t="str">
+      <c r="A80" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 078</v>
       </c>
-      <c r="B80" s="23"/>
-      <c r="C80" s="12"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="15"/>
-      <c r="H80" s="28"/>
-      <c r="I80" s="18"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
+      <c r="H80" s="21"/>
+      <c r="I80" s="15"/>
     </row>
     <row r="81" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A81" s="21" t="str">
+      <c r="A81" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 079</v>
       </c>
-      <c r="B81" s="23"/>
-      <c r="C81" s="12"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="15"/>
-      <c r="F81" s="15"/>
-      <c r="G81" s="15"/>
-      <c r="H81" s="28"/>
-      <c r="I81" s="18"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
+      <c r="H81" s="21"/>
+      <c r="I81" s="15"/>
     </row>
     <row r="82" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A82" s="21" t="str">
+      <c r="A82" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 080</v>
       </c>
-      <c r="B82" s="23"/>
-      <c r="C82" s="12"/>
-      <c r="D82" s="11"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15"/>
-      <c r="H82" s="28"/>
-      <c r="I82" s="18"/>
+      <c r="B82" s="9"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
+      <c r="H82" s="21"/>
+      <c r="I82" s="15"/>
     </row>
     <row r="83" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A83" s="21" t="str">
+      <c r="A83" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 081</v>
       </c>
-      <c r="B83" s="23"/>
-      <c r="C83" s="12"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="15"/>
-      <c r="F83" s="15"/>
-      <c r="G83" s="15"/>
-      <c r="H83" s="28"/>
-      <c r="I83" s="18"/>
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
+      <c r="H83" s="21"/>
+      <c r="I83" s="15"/>
     </row>
     <row r="84" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A84" s="21" t="str">
+      <c r="A84" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 082</v>
       </c>
-      <c r="B84" s="23"/>
-      <c r="C84" s="12"/>
-      <c r="D84" s="11"/>
-      <c r="E84" s="15"/>
-      <c r="F84" s="15"/>
-      <c r="G84" s="15"/>
-      <c r="H84" s="28"/>
-      <c r="I84" s="18"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="21"/>
+      <c r="I84" s="15"/>
     </row>
     <row r="85" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A85" s="21" t="str">
+      <c r="A85" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 083</v>
       </c>
-      <c r="B85" s="23"/>
-      <c r="C85" s="12"/>
-      <c r="D85" s="11"/>
-      <c r="E85" s="15"/>
-      <c r="F85" s="15"/>
-      <c r="G85" s="15"/>
-      <c r="H85" s="28"/>
-      <c r="I85" s="18"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
+      <c r="H85" s="21"/>
+      <c r="I85" s="15"/>
     </row>
     <row r="86" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A86" s="21" t="str">
+      <c r="A86" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 084</v>
       </c>
-      <c r="B86" s="23"/>
-      <c r="C86" s="12"/>
-      <c r="D86" s="11"/>
-      <c r="E86" s="15"/>
-      <c r="F86" s="15"/>
-      <c r="G86" s="15"/>
-      <c r="H86" s="28"/>
-      <c r="I86" s="18"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
+      <c r="H86" s="21"/>
+      <c r="I86" s="15"/>
     </row>
     <row r="87" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A87" s="21" t="str">
+      <c r="A87" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 085</v>
       </c>
-      <c r="B87" s="23"/>
-      <c r="C87" s="12"/>
-      <c r="D87" s="11"/>
-      <c r="E87" s="15"/>
-      <c r="F87" s="15"/>
-      <c r="G87" s="15"/>
-      <c r="H87" s="28"/>
-      <c r="I87" s="18"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="9"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+      <c r="H87" s="21"/>
+      <c r="I87" s="15"/>
     </row>
     <row r="88" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A88" s="21" t="str">
+      <c r="A88" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 086</v>
       </c>
-      <c r="B88" s="23"/>
-      <c r="C88" s="12"/>
-      <c r="D88" s="11"/>
-      <c r="E88" s="15"/>
-      <c r="F88" s="15"/>
-      <c r="G88" s="15"/>
-      <c r="H88" s="28"/>
-      <c r="I88" s="18"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="9"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
+      <c r="H88" s="21"/>
+      <c r="I88" s="15"/>
     </row>
     <row r="89" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A89" s="21" t="str">
+      <c r="A89" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 087</v>
       </c>
-      <c r="B89" s="23"/>
-      <c r="C89" s="12"/>
-      <c r="D89" s="11"/>
-      <c r="E89" s="15"/>
-      <c r="F89" s="15"/>
-      <c r="G89" s="15"/>
-      <c r="H89" s="28"/>
-      <c r="I89" s="18"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="9"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="12"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="12"/>
+      <c r="H89" s="21"/>
+      <c r="I89" s="15"/>
     </row>
     <row r="90" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A90" s="21" t="str">
+      <c r="A90" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 088</v>
       </c>
-      <c r="B90" s="23"/>
-      <c r="C90" s="12"/>
-      <c r="D90" s="11"/>
-      <c r="E90" s="15"/>
-      <c r="F90" s="15"/>
-      <c r="G90" s="15"/>
-      <c r="H90" s="28"/>
-      <c r="I90" s="18"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
+      <c r="H90" s="21"/>
+      <c r="I90" s="15"/>
     </row>
     <row r="91" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A91" s="21" t="str">
+      <c r="A91" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 089</v>
       </c>
-      <c r="B91" s="23"/>
-      <c r="C91" s="12"/>
-      <c r="D91" s="11"/>
-      <c r="E91" s="15"/>
-      <c r="F91" s="15"/>
-      <c r="G91" s="15"/>
-      <c r="H91" s="28"/>
-      <c r="I91" s="18"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="9"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
+      <c r="H91" s="21"/>
+      <c r="I91" s="15"/>
     </row>
     <row r="92" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A92" s="21" t="str">
+      <c r="A92" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 090</v>
       </c>
-      <c r="B92" s="23"/>
-      <c r="C92" s="12"/>
-      <c r="D92" s="11"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15"/>
-      <c r="H92" s="28"/>
-      <c r="I92" s="18"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="9"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
+      <c r="H92" s="21"/>
+      <c r="I92" s="15"/>
     </row>
     <row r="93" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A93" s="21" t="str">
+      <c r="A93" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 091</v>
       </c>
-      <c r="B93" s="23"/>
-      <c r="C93" s="12"/>
-      <c r="D93" s="11"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="15"/>
-      <c r="G93" s="15"/>
-      <c r="H93" s="28"/>
-      <c r="I93" s="18"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="9"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="21"/>
+      <c r="I93" s="15"/>
     </row>
     <row r="94" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A94" s="21" t="str">
+      <c r="A94" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 092</v>
       </c>
-      <c r="B94" s="23"/>
-      <c r="C94" s="12"/>
-      <c r="D94" s="11"/>
-      <c r="E94" s="15"/>
-      <c r="F94" s="15"/>
-      <c r="G94" s="15"/>
-      <c r="H94" s="28"/>
-      <c r="I94" s="18"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="8"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="21"/>
+      <c r="I94" s="15"/>
     </row>
     <row r="95" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A95" s="21" t="str">
+      <c r="A95" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 093</v>
       </c>
-      <c r="B95" s="23"/>
-      <c r="C95" s="12"/>
-      <c r="D95" s="11"/>
-      <c r="E95" s="15"/>
-      <c r="F95" s="15"/>
-      <c r="G95" s="15"/>
-      <c r="H95" s="28"/>
-      <c r="I95" s="18"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
+      <c r="H95" s="21"/>
+      <c r="I95" s="15"/>
     </row>
     <row r="96" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A96" s="21" t="str">
+      <c r="A96" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 094</v>
       </c>
-      <c r="B96" s="23"/>
-      <c r="C96" s="12"/>
-      <c r="D96" s="11"/>
-      <c r="E96" s="15"/>
-      <c r="F96" s="15"/>
-      <c r="G96" s="15"/>
-      <c r="H96" s="28"/>
-      <c r="I96" s="18"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="9"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
+      <c r="H96" s="21"/>
+      <c r="I96" s="15"/>
     </row>
     <row r="97" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A97" s="21" t="str">
+      <c r="A97" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 095</v>
       </c>
-      <c r="B97" s="23"/>
-      <c r="C97" s="12"/>
-      <c r="D97" s="11"/>
-      <c r="E97" s="15"/>
-      <c r="F97" s="15"/>
-      <c r="G97" s="15"/>
-      <c r="H97" s="28"/>
-      <c r="I97" s="18"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="9"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
+      <c r="H97" s="21"/>
+      <c r="I97" s="15"/>
     </row>
     <row r="98" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A98" s="21" t="str">
+      <c r="A98" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 096</v>
       </c>
-      <c r="B98" s="23"/>
-      <c r="C98" s="12"/>
-      <c r="D98" s="11"/>
-      <c r="E98" s="15"/>
-      <c r="F98" s="15"/>
-      <c r="G98" s="15"/>
-      <c r="H98" s="28"/>
-      <c r="I98" s="18"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="8"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
+      <c r="H98" s="21"/>
+      <c r="I98" s="15"/>
     </row>
     <row r="99" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A99" s="21" t="str">
+      <c r="A99" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 097</v>
       </c>
-      <c r="B99" s="23"/>
-      <c r="C99" s="12"/>
-      <c r="D99" s="11"/>
-      <c r="E99" s="15"/>
-      <c r="F99" s="15"/>
-      <c r="G99" s="15"/>
-      <c r="H99" s="28"/>
-      <c r="I99" s="18"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+      <c r="H99" s="21"/>
+      <c r="I99" s="15"/>
     </row>
     <row r="100" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A100" s="21" t="str">
+      <c r="A100" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 098</v>
       </c>
-      <c r="B100" s="23"/>
-      <c r="C100" s="12"/>
-      <c r="D100" s="11"/>
-      <c r="E100" s="15"/>
-      <c r="F100" s="15"/>
-      <c r="G100" s="15"/>
-      <c r="H100" s="28"/>
-      <c r="I100" s="18"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
+      <c r="H100" s="21"/>
+      <c r="I100" s="15"/>
     </row>
     <row r="101" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A101" s="21" t="str">
+      <c r="A101" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 099</v>
       </c>
-      <c r="B101" s="23"/>
-      <c r="C101" s="12"/>
-      <c r="D101" s="11"/>
-      <c r="E101" s="15"/>
-      <c r="F101" s="15"/>
-      <c r="G101" s="15"/>
-      <c r="H101" s="28"/>
-      <c r="I101" s="18"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="12"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
+      <c r="H101" s="21"/>
+      <c r="I101" s="15"/>
     </row>
     <row r="102" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A102" s="21" t="str">
+      <c r="A102" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 100</v>
       </c>
-      <c r="B102" s="23"/>
-      <c r="C102" s="12"/>
-      <c r="D102" s="11"/>
-      <c r="E102" s="15"/>
-      <c r="F102" s="15"/>
-      <c r="G102" s="15"/>
-      <c r="H102" s="28"/>
-      <c r="I102" s="18"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="9"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="12"/>
+      <c r="F102" s="12"/>
+      <c r="G102" s="12"/>
+      <c r="H102" s="21"/>
+      <c r="I102" s="15"/>
     </row>
     <row r="103" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A103" s="21" t="str">
+      <c r="A103" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 101</v>
       </c>
-      <c r="B103" s="23"/>
-      <c r="C103" s="12"/>
-      <c r="D103" s="11"/>
-      <c r="E103" s="15"/>
-      <c r="F103" s="15"/>
-      <c r="G103" s="15"/>
-      <c r="H103" s="28"/>
-      <c r="I103" s="18"/>
+      <c r="B103" s="9"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="12"/>
+      <c r="F103" s="12"/>
+      <c r="G103" s="12"/>
+      <c r="H103" s="21"/>
+      <c r="I103" s="15"/>
     </row>
     <row r="104" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A104" s="21" t="str">
+      <c r="A104" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 102</v>
       </c>
-      <c r="B104" s="23"/>
-      <c r="C104" s="12"/>
-      <c r="D104" s="11"/>
-      <c r="E104" s="15"/>
-      <c r="F104" s="15"/>
-      <c r="G104" s="15"/>
-      <c r="H104" s="28"/>
-      <c r="I104" s="18"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="9"/>
+      <c r="D104" s="8"/>
+      <c r="E104" s="12"/>
+      <c r="F104" s="12"/>
+      <c r="G104" s="12"/>
+      <c r="H104" s="21"/>
+      <c r="I104" s="15"/>
     </row>
     <row r="105" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A105" s="21" t="str">
+      <c r="A105" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 103</v>
       </c>
-      <c r="B105" s="23"/>
-      <c r="C105" s="12"/>
-      <c r="D105" s="11"/>
-      <c r="E105" s="15"/>
-      <c r="F105" s="15"/>
-      <c r="G105" s="15"/>
-      <c r="H105" s="28"/>
-      <c r="I105" s="18"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="9"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="12"/>
+      <c r="G105" s="12"/>
+      <c r="H105" s="21"/>
+      <c r="I105" s="15"/>
     </row>
     <row r="106" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A106" s="21" t="str">
+      <c r="A106" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 104</v>
       </c>
-      <c r="B106" s="23"/>
-      <c r="C106" s="12"/>
-      <c r="D106" s="11"/>
-      <c r="E106" s="15"/>
-      <c r="F106" s="15"/>
-      <c r="G106" s="15"/>
-      <c r="H106" s="28"/>
-      <c r="I106" s="18"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="9"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
+      <c r="H106" s="21"/>
+      <c r="I106" s="15"/>
     </row>
     <row r="107" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A107" s="21" t="str">
+      <c r="A107" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 105</v>
       </c>
-      <c r="B107" s="23"/>
-      <c r="C107" s="12"/>
-      <c r="D107" s="11"/>
-      <c r="E107" s="15"/>
-      <c r="F107" s="15"/>
-      <c r="G107" s="15"/>
-      <c r="H107" s="28"/>
-      <c r="I107" s="18"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="9"/>
+      <c r="D107" s="8"/>
+      <c r="E107" s="12"/>
+      <c r="F107" s="12"/>
+      <c r="G107" s="12"/>
+      <c r="H107" s="21"/>
+      <c r="I107" s="15"/>
     </row>
     <row r="108" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A108" s="21" t="str">
+      <c r="A108" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 106</v>
       </c>
-      <c r="B108" s="23"/>
-      <c r="C108" s="12"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="15"/>
-      <c r="F108" s="15"/>
-      <c r="G108" s="15"/>
-      <c r="H108" s="28"/>
-      <c r="I108" s="18"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="12"/>
+      <c r="F108" s="12"/>
+      <c r="G108" s="12"/>
+      <c r="H108" s="21"/>
+      <c r="I108" s="15"/>
     </row>
     <row r="109" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A109" s="21" t="str">
+      <c r="A109" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 107</v>
       </c>
-      <c r="B109" s="23"/>
-      <c r="C109" s="12"/>
-      <c r="D109" s="11"/>
-      <c r="E109" s="15"/>
-      <c r="F109" s="15"/>
-      <c r="G109" s="15"/>
-      <c r="H109" s="28"/>
-      <c r="I109" s="18"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="8"/>
+      <c r="E109" s="12"/>
+      <c r="F109" s="12"/>
+      <c r="G109" s="12"/>
+      <c r="H109" s="21"/>
+      <c r="I109" s="15"/>
     </row>
     <row r="110" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A110" s="21" t="str">
+      <c r="A110" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 108</v>
       </c>
-      <c r="B110" s="23"/>
-      <c r="C110" s="12"/>
-      <c r="D110" s="11"/>
-      <c r="E110" s="15"/>
-      <c r="F110" s="15"/>
-      <c r="G110" s="15"/>
-      <c r="H110" s="28"/>
-      <c r="I110" s="18"/>
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="8"/>
+      <c r="E110" s="12"/>
+      <c r="F110" s="12"/>
+      <c r="G110" s="12"/>
+      <c r="H110" s="21"/>
+      <c r="I110" s="15"/>
     </row>
     <row r="111" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A111" s="21" t="str">
+      <c r="A111" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 109</v>
       </c>
-      <c r="B111" s="23"/>
-      <c r="C111" s="12"/>
-      <c r="D111" s="11"/>
-      <c r="E111" s="15"/>
-      <c r="F111" s="15"/>
-      <c r="G111" s="15"/>
-      <c r="H111" s="28"/>
-      <c r="I111" s="18"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+      <c r="D111" s="8"/>
+      <c r="E111" s="12"/>
+      <c r="F111" s="12"/>
+      <c r="G111" s="12"/>
+      <c r="H111" s="21"/>
+      <c r="I111" s="15"/>
     </row>
     <row r="112" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A112" s="21" t="str">
+      <c r="A112" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 110</v>
       </c>
-      <c r="B112" s="23"/>
-      <c r="C112" s="12"/>
-      <c r="D112" s="11"/>
-      <c r="E112" s="15"/>
-      <c r="F112" s="15"/>
-      <c r="G112" s="15"/>
-      <c r="H112" s="28"/>
-      <c r="I112" s="18"/>
+      <c r="B112" s="9"/>
+      <c r="C112" s="9"/>
+      <c r="D112" s="8"/>
+      <c r="E112" s="12"/>
+      <c r="F112" s="12"/>
+      <c r="G112" s="12"/>
+      <c r="H112" s="21"/>
+      <c r="I112" s="15"/>
     </row>
     <row r="113" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A113" s="21" t="str">
+      <c r="A113" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 111</v>
       </c>
-      <c r="B113" s="23"/>
-      <c r="C113" s="12"/>
-      <c r="D113" s="11"/>
-      <c r="E113" s="15"/>
-      <c r="F113" s="15"/>
-      <c r="G113" s="15"/>
-      <c r="H113" s="28"/>
-      <c r="I113" s="18"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
+      <c r="D113" s="8"/>
+      <c r="E113" s="12"/>
+      <c r="F113" s="12"/>
+      <c r="G113" s="12"/>
+      <c r="H113" s="21"/>
+      <c r="I113" s="15"/>
     </row>
     <row r="114" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A114" s="21" t="str">
+      <c r="A114" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 112</v>
       </c>
-      <c r="B114" s="23"/>
-      <c r="C114" s="12"/>
-      <c r="D114" s="11"/>
-      <c r="E114" s="15"/>
-      <c r="F114" s="15"/>
-      <c r="G114" s="15"/>
-      <c r="H114" s="28"/>
-      <c r="I114" s="18"/>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9"/>
+      <c r="D114" s="8"/>
+      <c r="E114" s="12"/>
+      <c r="F114" s="12"/>
+      <c r="G114" s="12"/>
+      <c r="H114" s="21"/>
+      <c r="I114" s="15"/>
     </row>
     <row r="115" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A115" s="21" t="str">
+      <c r="A115" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 113</v>
       </c>
-      <c r="B115" s="23"/>
-      <c r="C115" s="12"/>
-      <c r="D115" s="11"/>
-      <c r="E115" s="15"/>
-      <c r="F115" s="15"/>
-      <c r="G115" s="15"/>
-      <c r="H115" s="28"/>
-      <c r="I115" s="18"/>
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
+      <c r="D115" s="8"/>
+      <c r="E115" s="12"/>
+      <c r="F115" s="12"/>
+      <c r="G115" s="12"/>
+      <c r="H115" s="21"/>
+      <c r="I115" s="15"/>
     </row>
     <row r="116" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A116" s="21" t="str">
+      <c r="A116" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 114</v>
       </c>
-      <c r="B116" s="23"/>
-      <c r="C116" s="12"/>
-      <c r="D116" s="11"/>
-      <c r="E116" s="15"/>
-      <c r="F116" s="15"/>
-      <c r="G116" s="15"/>
-      <c r="H116" s="28"/>
-      <c r="I116" s="18"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="9"/>
+      <c r="D116" s="8"/>
+      <c r="E116" s="12"/>
+      <c r="F116" s="12"/>
+      <c r="G116" s="12"/>
+      <c r="H116" s="21"/>
+      <c r="I116" s="15"/>
     </row>
     <row r="117" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A117" s="21" t="str">
+      <c r="A117" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 115</v>
       </c>
-      <c r="B117" s="23"/>
-      <c r="C117" s="12"/>
-      <c r="D117" s="11"/>
-      <c r="E117" s="15"/>
-      <c r="F117" s="15"/>
-      <c r="G117" s="15"/>
-      <c r="H117" s="28"/>
-      <c r="I117" s="18"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="9"/>
+      <c r="D117" s="8"/>
+      <c r="E117" s="12"/>
+      <c r="F117" s="12"/>
+      <c r="G117" s="12"/>
+      <c r="H117" s="21"/>
+      <c r="I117" s="15"/>
     </row>
     <row r="118" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A118" s="21" t="str">
+      <c r="A118" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 116</v>
       </c>
-      <c r="B118" s="23"/>
-      <c r="C118" s="12"/>
-      <c r="D118" s="11"/>
-      <c r="E118" s="15"/>
-      <c r="F118" s="15"/>
-      <c r="G118" s="15"/>
-      <c r="H118" s="28"/>
-      <c r="I118" s="18"/>
+      <c r="B118" s="9"/>
+      <c r="C118" s="9"/>
+      <c r="D118" s="8"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
+      <c r="H118" s="21"/>
+      <c r="I118" s="15"/>
     </row>
     <row r="119" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A119" s="21" t="str">
+      <c r="A119" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 117</v>
       </c>
-      <c r="B119" s="23"/>
-      <c r="C119" s="12"/>
-      <c r="D119" s="11"/>
-      <c r="E119" s="15"/>
-      <c r="F119" s="15"/>
-      <c r="G119" s="15"/>
-      <c r="H119" s="28"/>
-      <c r="I119" s="18"/>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
+      <c r="D119" s="8"/>
+      <c r="E119" s="12"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="12"/>
+      <c r="H119" s="21"/>
+      <c r="I119" s="15"/>
     </row>
     <row r="120" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A120" s="21" t="str">
+      <c r="A120" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 118</v>
       </c>
-      <c r="B120" s="23"/>
-      <c r="C120" s="12"/>
-      <c r="D120" s="11"/>
-      <c r="E120" s="15"/>
-      <c r="F120" s="15"/>
-      <c r="G120" s="15"/>
-      <c r="H120" s="28"/>
-      <c r="I120" s="18"/>
+      <c r="B120" s="9"/>
+      <c r="C120" s="9"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="12"/>
+      <c r="F120" s="12"/>
+      <c r="G120" s="12"/>
+      <c r="H120" s="21"/>
+      <c r="I120" s="15"/>
     </row>
     <row r="121" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A121" s="21" t="str">
+      <c r="A121" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 119</v>
       </c>
-      <c r="B121" s="23"/>
-      <c r="C121" s="12"/>
-      <c r="D121" s="11"/>
-      <c r="E121" s="15"/>
-      <c r="F121" s="15"/>
-      <c r="G121" s="15"/>
-      <c r="H121" s="28"/>
-      <c r="I121" s="18"/>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
+      <c r="D121" s="8"/>
+      <c r="E121" s="12"/>
+      <c r="F121" s="12"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="21"/>
+      <c r="I121" s="15"/>
     </row>
     <row r="122" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A122" s="21" t="str">
+      <c r="A122" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 120</v>
       </c>
-      <c r="B122" s="23"/>
-      <c r="C122" s="12"/>
-      <c r="D122" s="11"/>
-      <c r="E122" s="15"/>
-      <c r="F122" s="15"/>
-      <c r="G122" s="15"/>
-      <c r="H122" s="28"/>
-      <c r="I122" s="18"/>
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+      <c r="D122" s="8"/>
+      <c r="E122" s="12"/>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="21"/>
+      <c r="I122" s="15"/>
     </row>
     <row r="123" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A123" s="21" t="str">
+      <c r="A123" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 121</v>
       </c>
-      <c r="B123" s="23"/>
-      <c r="C123" s="12"/>
-      <c r="D123" s="11"/>
-      <c r="E123" s="15"/>
-      <c r="F123" s="15"/>
-      <c r="G123" s="15"/>
-      <c r="H123" s="28"/>
-      <c r="I123" s="18"/>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="8"/>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="21"/>
+      <c r="I123" s="15"/>
     </row>
     <row r="124" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A124" s="21" t="str">
+      <c r="A124" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 122</v>
       </c>
-      <c r="B124" s="23"/>
-      <c r="C124" s="12"/>
-      <c r="D124" s="11"/>
-      <c r="E124" s="15"/>
-      <c r="F124" s="15"/>
-      <c r="G124" s="15"/>
-      <c r="H124" s="28"/>
-      <c r="I124" s="18"/>
+      <c r="B124" s="9"/>
+      <c r="C124" s="9"/>
+      <c r="D124" s="8"/>
+      <c r="E124" s="12"/>
+      <c r="F124" s="12"/>
+      <c r="G124" s="12"/>
+      <c r="H124" s="21"/>
+      <c r="I124" s="15"/>
     </row>
     <row r="125" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A125" s="21" t="str">
+      <c r="A125" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 123</v>
       </c>
-      <c r="B125" s="23"/>
-      <c r="C125" s="12"/>
-      <c r="D125" s="11"/>
-      <c r="E125" s="15"/>
-      <c r="F125" s="15"/>
-      <c r="G125" s="15"/>
-      <c r="H125" s="28"/>
-      <c r="I125" s="18"/>
+      <c r="B125" s="9"/>
+      <c r="C125" s="9"/>
+      <c r="D125" s="8"/>
+      <c r="E125" s="12"/>
+      <c r="F125" s="12"/>
+      <c r="G125" s="12"/>
+      <c r="H125" s="21"/>
+      <c r="I125" s="15"/>
     </row>
     <row r="126" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A126" s="21" t="str">
+      <c r="A126" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 124</v>
       </c>
-      <c r="B126" s="23"/>
-      <c r="C126" s="12"/>
-      <c r="D126" s="11"/>
-      <c r="E126" s="15"/>
-      <c r="F126" s="15"/>
-      <c r="G126" s="15"/>
-      <c r="H126" s="28"/>
-      <c r="I126" s="18"/>
+      <c r="B126" s="9"/>
+      <c r="C126" s="9"/>
+      <c r="D126" s="8"/>
+      <c r="E126" s="12"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12"/>
+      <c r="H126" s="21"/>
+      <c r="I126" s="15"/>
     </row>
     <row r="127" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A127" s="21" t="str">
+      <c r="A127" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 125</v>
       </c>
-      <c r="B127" s="23"/>
-      <c r="C127" s="12"/>
-      <c r="D127" s="11"/>
-      <c r="E127" s="15"/>
-      <c r="F127" s="15"/>
-      <c r="G127" s="15"/>
-      <c r="H127" s="28"/>
-      <c r="I127" s="18"/>
+      <c r="B127" s="9"/>
+      <c r="C127" s="9"/>
+      <c r="D127" s="8"/>
+      <c r="E127" s="12"/>
+      <c r="F127" s="12"/>
+      <c r="G127" s="12"/>
+      <c r="H127" s="21"/>
+      <c r="I127" s="15"/>
     </row>
     <row r="128" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A128" s="21" t="str">
+      <c r="A128" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 126</v>
       </c>
-      <c r="B128" s="23"/>
-      <c r="C128" s="12"/>
-      <c r="D128" s="11"/>
-      <c r="E128" s="15"/>
-      <c r="F128" s="15"/>
-      <c r="G128" s="15"/>
-      <c r="H128" s="28"/>
-      <c r="I128" s="18"/>
+      <c r="B128" s="9"/>
+      <c r="C128" s="9"/>
+      <c r="D128" s="8"/>
+      <c r="E128" s="12"/>
+      <c r="F128" s="12"/>
+      <c r="G128" s="12"/>
+      <c r="H128" s="21"/>
+      <c r="I128" s="15"/>
     </row>
     <row r="129" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A129" s="21" t="str">
+      <c r="A129" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 127</v>
       </c>
-      <c r="B129" s="23"/>
-      <c r="C129" s="12"/>
-      <c r="D129" s="11"/>
-      <c r="E129" s="15"/>
-      <c r="F129" s="15"/>
-      <c r="G129" s="15"/>
-      <c r="H129" s="28"/>
-      <c r="I129" s="18"/>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="8"/>
+      <c r="E129" s="12"/>
+      <c r="F129" s="12"/>
+      <c r="G129" s="12"/>
+      <c r="H129" s="21"/>
+      <c r="I129" s="15"/>
     </row>
     <row r="130" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A130" s="21" t="str">
+      <c r="A130" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 128</v>
       </c>
-      <c r="B130" s="23"/>
-      <c r="C130" s="12"/>
-      <c r="D130" s="11"/>
-      <c r="E130" s="15"/>
-      <c r="F130" s="15"/>
-      <c r="G130" s="15"/>
-      <c r="H130" s="28"/>
-      <c r="I130" s="18"/>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="8"/>
+      <c r="E130" s="12"/>
+      <c r="F130" s="12"/>
+      <c r="G130" s="12"/>
+      <c r="H130" s="21"/>
+      <c r="I130" s="15"/>
     </row>
     <row r="131" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A131" s="21" t="str">
+      <c r="A131" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Test 129</v>
       </c>
-      <c r="B131" s="23"/>
-      <c r="C131" s="12"/>
-      <c r="D131" s="11"/>
-      <c r="E131" s="15"/>
-      <c r="F131" s="15"/>
-      <c r="G131" s="15"/>
-      <c r="H131" s="28"/>
-      <c r="I131" s="18"/>
+      <c r="B131" s="9"/>
+      <c r="C131" s="9"/>
+      <c r="D131" s="8"/>
+      <c r="E131" s="12"/>
+      <c r="F131" s="12"/>
+      <c r="G131" s="12"/>
+      <c r="H131" s="21"/>
+      <c r="I131" s="15"/>
     </row>
     <row r="132" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A132" s="21" t="str">
+      <c r="A132" s="18" t="str">
         <f t="shared" ref="A132:A152" si="2">"Test "&amp;TEXT(ROW()-2,"000")</f>
         <v>Test 130</v>
       </c>
-      <c r="B132" s="23"/>
-      <c r="C132" s="12"/>
-      <c r="D132" s="11"/>
-      <c r="E132" s="15"/>
-      <c r="F132" s="15"/>
-      <c r="G132" s="15"/>
-      <c r="H132" s="28"/>
-      <c r="I132" s="18"/>
+      <c r="B132" s="9"/>
+      <c r="C132" s="9"/>
+      <c r="D132" s="8"/>
+      <c r="E132" s="12"/>
+      <c r="F132" s="12"/>
+      <c r="G132" s="12"/>
+      <c r="H132" s="21"/>
+      <c r="I132" s="15"/>
     </row>
     <row r="133" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A133" s="21" t="str">
+      <c r="A133" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 131</v>
       </c>
-      <c r="B133" s="23"/>
-      <c r="C133" s="12"/>
-      <c r="D133" s="11"/>
-      <c r="E133" s="15"/>
-      <c r="F133" s="15"/>
-      <c r="G133" s="15"/>
-      <c r="H133" s="28"/>
-      <c r="I133" s="18"/>
+      <c r="B133" s="9"/>
+      <c r="C133" s="9"/>
+      <c r="D133" s="8"/>
+      <c r="E133" s="12"/>
+      <c r="F133" s="12"/>
+      <c r="G133" s="12"/>
+      <c r="H133" s="21"/>
+      <c r="I133" s="15"/>
     </row>
     <row r="134" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A134" s="21" t="str">
+      <c r="A134" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 132</v>
       </c>
-      <c r="B134" s="23"/>
-      <c r="C134" s="12"/>
-      <c r="D134" s="11"/>
-      <c r="E134" s="15"/>
-      <c r="F134" s="15"/>
-      <c r="G134" s="15"/>
-      <c r="H134" s="28"/>
-      <c r="I134" s="18"/>
+      <c r="B134" s="9"/>
+      <c r="C134" s="9"/>
+      <c r="D134" s="8"/>
+      <c r="E134" s="12"/>
+      <c r="F134" s="12"/>
+      <c r="G134" s="12"/>
+      <c r="H134" s="21"/>
+      <c r="I134" s="15"/>
     </row>
     <row r="135" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A135" s="21" t="str">
+      <c r="A135" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 133</v>
       </c>
-      <c r="B135" s="23"/>
-      <c r="C135" s="12"/>
-      <c r="D135" s="11"/>
-      <c r="E135" s="15"/>
-      <c r="F135" s="15"/>
-      <c r="G135" s="15"/>
-      <c r="H135" s="28"/>
-      <c r="I135" s="18"/>
+      <c r="B135" s="9"/>
+      <c r="C135" s="9"/>
+      <c r="D135" s="8"/>
+      <c r="E135" s="12"/>
+      <c r="F135" s="12"/>
+      <c r="G135" s="12"/>
+      <c r="H135" s="21"/>
+      <c r="I135" s="15"/>
     </row>
     <row r="136" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A136" s="21" t="str">
+      <c r="A136" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 134</v>
       </c>
-      <c r="B136" s="23"/>
-      <c r="C136" s="12"/>
-      <c r="D136" s="11"/>
-      <c r="E136" s="15"/>
-      <c r="F136" s="15"/>
-      <c r="G136" s="15"/>
-      <c r="H136" s="28"/>
-      <c r="I136" s="18"/>
+      <c r="B136" s="9"/>
+      <c r="C136" s="9"/>
+      <c r="D136" s="8"/>
+      <c r="E136" s="12"/>
+      <c r="F136" s="12"/>
+      <c r="G136" s="12"/>
+      <c r="H136" s="21"/>
+      <c r="I136" s="15"/>
     </row>
     <row r="137" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A137" s="21" t="str">
+      <c r="A137" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 135</v>
       </c>
-      <c r="B137" s="23"/>
-      <c r="C137" s="12"/>
-      <c r="D137" s="11"/>
-      <c r="E137" s="15"/>
-      <c r="F137" s="15"/>
-      <c r="G137" s="15"/>
-      <c r="H137" s="28"/>
-      <c r="I137" s="18"/>
+      <c r="B137" s="9"/>
+      <c r="C137" s="9"/>
+      <c r="D137" s="8"/>
+      <c r="E137" s="12"/>
+      <c r="F137" s="12"/>
+      <c r="G137" s="12"/>
+      <c r="H137" s="21"/>
+      <c r="I137" s="15"/>
     </row>
     <row r="138" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A138" s="21" t="str">
+      <c r="A138" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 136</v>
       </c>
-      <c r="B138" s="23"/>
-      <c r="C138" s="12"/>
-      <c r="D138" s="11"/>
-      <c r="E138" s="15"/>
-      <c r="F138" s="15"/>
-      <c r="G138" s="15"/>
-      <c r="H138" s="28"/>
-      <c r="I138" s="18"/>
+      <c r="B138" s="9"/>
+      <c r="C138" s="9"/>
+      <c r="D138" s="8"/>
+      <c r="E138" s="12"/>
+      <c r="F138" s="12"/>
+      <c r="G138" s="12"/>
+      <c r="H138" s="21"/>
+      <c r="I138" s="15"/>
     </row>
     <row r="139" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A139" s="21" t="str">
+      <c r="A139" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 137</v>
       </c>
-      <c r="B139" s="23"/>
-      <c r="C139" s="12"/>
-      <c r="D139" s="11"/>
-      <c r="E139" s="15"/>
-      <c r="F139" s="15"/>
-      <c r="G139" s="15"/>
-      <c r="H139" s="28"/>
-      <c r="I139" s="18"/>
+      <c r="B139" s="9"/>
+      <c r="C139" s="9"/>
+      <c r="D139" s="8"/>
+      <c r="E139" s="12"/>
+      <c r="F139" s="12"/>
+      <c r="G139" s="12"/>
+      <c r="H139" s="21"/>
+      <c r="I139" s="15"/>
     </row>
     <row r="140" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A140" s="21" t="str">
+      <c r="A140" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 138</v>
       </c>
-      <c r="B140" s="23"/>
-      <c r="C140" s="12"/>
-      <c r="D140" s="11"/>
-      <c r="E140" s="15"/>
-      <c r="F140" s="15"/>
-      <c r="G140" s="15"/>
-      <c r="H140" s="28"/>
-      <c r="I140" s="18"/>
+      <c r="B140" s="9"/>
+      <c r="C140" s="9"/>
+      <c r="D140" s="8"/>
+      <c r="E140" s="12"/>
+      <c r="F140" s="12"/>
+      <c r="G140" s="12"/>
+      <c r="H140" s="21"/>
+      <c r="I140" s="15"/>
     </row>
     <row r="141" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A141" s="21" t="str">
+      <c r="A141" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 139</v>
       </c>
-      <c r="B141" s="23"/>
-      <c r="C141" s="12"/>
-      <c r="D141" s="11"/>
-      <c r="E141" s="15"/>
-      <c r="F141" s="15"/>
-      <c r="G141" s="15"/>
-      <c r="H141" s="28"/>
-      <c r="I141" s="18"/>
+      <c r="B141" s="9"/>
+      <c r="C141" s="9"/>
+      <c r="D141" s="8"/>
+      <c r="E141" s="12"/>
+      <c r="F141" s="12"/>
+      <c r="G141" s="12"/>
+      <c r="H141" s="21"/>
+      <c r="I141" s="15"/>
     </row>
     <row r="142" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A142" s="21" t="str">
+      <c r="A142" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 140</v>
       </c>
-      <c r="B142" s="23"/>
-      <c r="C142" s="12"/>
-      <c r="D142" s="11"/>
-      <c r="E142" s="15"/>
-      <c r="F142" s="15"/>
-      <c r="G142" s="15"/>
-      <c r="H142" s="28"/>
-      <c r="I142" s="18"/>
+      <c r="B142" s="9"/>
+      <c r="C142" s="9"/>
+      <c r="D142" s="8"/>
+      <c r="E142" s="12"/>
+      <c r="F142" s="12"/>
+      <c r="G142" s="12"/>
+      <c r="H142" s="21"/>
+      <c r="I142" s="15"/>
     </row>
     <row r="143" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A143" s="21" t="str">
+      <c r="A143" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 141</v>
       </c>
-      <c r="B143" s="23"/>
-      <c r="C143" s="12"/>
-      <c r="D143" s="11"/>
-      <c r="E143" s="15"/>
-      <c r="F143" s="15"/>
-      <c r="G143" s="15"/>
-      <c r="H143" s="28"/>
-      <c r="I143" s="18"/>
+      <c r="B143" s="9"/>
+      <c r="C143" s="9"/>
+      <c r="D143" s="8"/>
+      <c r="E143" s="12"/>
+      <c r="F143" s="12"/>
+      <c r="G143" s="12"/>
+      <c r="H143" s="21"/>
+      <c r="I143" s="15"/>
     </row>
     <row r="144" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A144" s="21" t="str">
+      <c r="A144" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 142</v>
       </c>
-      <c r="B144" s="23"/>
-      <c r="C144" s="12"/>
-      <c r="D144" s="11"/>
-      <c r="E144" s="15"/>
-      <c r="F144" s="15"/>
-      <c r="G144" s="15"/>
-      <c r="H144" s="28"/>
-      <c r="I144" s="18"/>
+      <c r="B144" s="9"/>
+      <c r="C144" s="9"/>
+      <c r="D144" s="8"/>
+      <c r="E144" s="12"/>
+      <c r="F144" s="12"/>
+      <c r="G144" s="12"/>
+      <c r="H144" s="21"/>
+      <c r="I144" s="15"/>
     </row>
     <row r="145" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A145" s="21" t="str">
+      <c r="A145" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 143</v>
       </c>
-      <c r="B145" s="23"/>
-      <c r="C145" s="12"/>
-      <c r="D145" s="11"/>
-      <c r="E145" s="15"/>
-      <c r="F145" s="15"/>
-      <c r="G145" s="15"/>
-      <c r="H145" s="28"/>
-      <c r="I145" s="18"/>
+      <c r="B145" s="9"/>
+      <c r="C145" s="9"/>
+      <c r="D145" s="8"/>
+      <c r="E145" s="12"/>
+      <c r="F145" s="12"/>
+      <c r="G145" s="12"/>
+      <c r="H145" s="21"/>
+      <c r="I145" s="15"/>
     </row>
     <row r="146" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A146" s="21" t="str">
+      <c r="A146" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 144</v>
       </c>
-      <c r="B146" s="23"/>
-      <c r="C146" s="12"/>
-      <c r="D146" s="11"/>
-      <c r="E146" s="15"/>
-      <c r="F146" s="15"/>
-      <c r="G146" s="15"/>
-      <c r="H146" s="28"/>
-      <c r="I146" s="18"/>
+      <c r="B146" s="9"/>
+      <c r="C146" s="9"/>
+      <c r="D146" s="8"/>
+      <c r="E146" s="12"/>
+      <c r="F146" s="12"/>
+      <c r="G146" s="12"/>
+      <c r="H146" s="21"/>
+      <c r="I146" s="15"/>
     </row>
     <row r="147" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A147" s="21" t="str">
+      <c r="A147" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 145</v>
       </c>
-      <c r="B147" s="23"/>
-      <c r="C147" s="12"/>
-      <c r="D147" s="11"/>
-      <c r="E147" s="15"/>
-      <c r="F147" s="15"/>
-      <c r="G147" s="15"/>
-      <c r="H147" s="28"/>
-      <c r="I147" s="18"/>
+      <c r="B147" s="9"/>
+      <c r="C147" s="9"/>
+      <c r="D147" s="8"/>
+      <c r="E147" s="12"/>
+      <c r="F147" s="12"/>
+      <c r="G147" s="12"/>
+      <c r="H147" s="21"/>
+      <c r="I147" s="15"/>
     </row>
     <row r="148" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A148" s="21" t="str">
+      <c r="A148" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 146</v>
       </c>
-      <c r="B148" s="23"/>
-      <c r="C148" s="12"/>
-      <c r="D148" s="11"/>
-      <c r="E148" s="15"/>
-      <c r="F148" s="15"/>
-      <c r="G148" s="15"/>
-      <c r="H148" s="28"/>
-      <c r="I148" s="18"/>
+      <c r="B148" s="9"/>
+      <c r="C148" s="9"/>
+      <c r="D148" s="8"/>
+      <c r="E148" s="12"/>
+      <c r="F148" s="12"/>
+      <c r="G148" s="12"/>
+      <c r="H148" s="21"/>
+      <c r="I148" s="15"/>
     </row>
     <row r="149" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A149" s="21" t="str">
+      <c r="A149" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 147</v>
       </c>
-      <c r="B149" s="23"/>
-      <c r="C149" s="12"/>
-      <c r="D149" s="11"/>
-      <c r="E149" s="15"/>
-      <c r="F149" s="15"/>
-      <c r="G149" s="15"/>
-      <c r="H149" s="28"/>
-      <c r="I149" s="18"/>
+      <c r="B149" s="9"/>
+      <c r="C149" s="9"/>
+      <c r="D149" s="8"/>
+      <c r="E149" s="12"/>
+      <c r="F149" s="12"/>
+      <c r="G149" s="12"/>
+      <c r="H149" s="21"/>
+      <c r="I149" s="15"/>
     </row>
     <row r="150" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A150" s="21" t="str">
+      <c r="A150" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 148</v>
       </c>
-      <c r="B150" s="23"/>
-      <c r="C150" s="12"/>
-      <c r="D150" s="11"/>
-      <c r="E150" s="15"/>
-      <c r="F150" s="15"/>
-      <c r="G150" s="15"/>
-      <c r="H150" s="28"/>
-      <c r="I150" s="18"/>
+      <c r="B150" s="9"/>
+      <c r="C150" s="9"/>
+      <c r="D150" s="8"/>
+      <c r="E150" s="12"/>
+      <c r="F150" s="12"/>
+      <c r="G150" s="12"/>
+      <c r="H150" s="21"/>
+      <c r="I150" s="15"/>
     </row>
     <row r="151" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A151" s="21" t="str">
+      <c r="A151" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 149</v>
       </c>
-      <c r="B151" s="23"/>
-      <c r="C151" s="12"/>
-      <c r="D151" s="11"/>
-      <c r="E151" s="15"/>
-      <c r="F151" s="15"/>
-      <c r="G151" s="15"/>
-      <c r="H151" s="28"/>
-      <c r="I151" s="18"/>
+      <c r="B151" s="9"/>
+      <c r="C151" s="9"/>
+      <c r="D151" s="8"/>
+      <c r="E151" s="12"/>
+      <c r="F151" s="12"/>
+      <c r="G151" s="12"/>
+      <c r="H151" s="21"/>
+      <c r="I151" s="15"/>
     </row>
     <row r="152" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A152" s="21" t="str">
+      <c r="A152" s="18" t="str">
         <f t="shared" si="2"/>
         <v>Test 150</v>
       </c>
-      <c r="B152" s="23"/>
-      <c r="C152" s="12"/>
-      <c r="D152" s="11"/>
-      <c r="E152" s="15"/>
-      <c r="F152" s="15"/>
-      <c r="G152" s="15"/>
-      <c r="H152" s="28"/>
-      <c r="I152" s="18"/>
+      <c r="B152" s="9"/>
+      <c r="C152" s="9"/>
+      <c r="D152" s="8"/>
+      <c r="E152" s="12"/>
+      <c r="F152" s="12"/>
+      <c r="G152" s="12"/>
+      <c r="H152" s="21"/>
+      <c r="I152" s="15"/>
     </row>
     <row r="153" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A153" s="21"/>
-      <c r="B153" s="24"/>
-      <c r="C153" s="13"/>
-      <c r="D153" s="1"/>
-      <c r="E153" s="15"/>
-      <c r="F153" s="15"/>
-      <c r="G153" s="15"/>
-      <c r="H153" s="28"/>
-      <c r="I153" s="18"/>
+      <c r="A153" s="18"/>
+      <c r="B153" s="10"/>
+      <c r="C153" s="10"/>
+      <c r="E153" s="12"/>
+      <c r="F153" s="12"/>
+      <c r="G153" s="12"/>
+      <c r="H153" s="21"/>
+      <c r="I153" s="15"/>
     </row>
     <row r="154" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A154" s="22"/>
-      <c r="B154" s="25"/>
-      <c r="C154" s="14"/>
+      <c r="A154" s="19"/>
+      <c r="B154" s="11"/>
+      <c r="C154" s="11"/>
       <c r="D154" s="2"/>
-      <c r="E154" s="19"/>
-      <c r="F154" s="19"/>
-      <c r="G154" s="19"/>
-      <c r="H154" s="19"/>
-      <c r="I154" s="20"/>
+      <c r="E154" s="16"/>
+      <c r="F154" s="16"/>
+      <c r="G154" s="16"/>
+      <c r="H154" s="16"/>
+      <c r="I154" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>
   </mergeCells>
+  <conditionalFormatting sqref="E3:F152">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Spam">
+      <formula>NOT(ISERROR(SEARCH("Spam",E3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Legitmate">
+      <formula>NOT(ISERROR(SEARCH("Legitmate",E3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Phishing">
+      <formula>NOT(ISERROR(SEARCH("Phishing",E3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I3:I152">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",I3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH("Fail",I3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3:F152">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Spam">
-      <formula>NOT(ISERROR(SEARCH("Spam",E3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Legitmate">
-      <formula>NOT(ISERROR(SEARCH("Legitmate",E3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Phishing">
-      <formula>NOT(ISERROR(SEARCH("Phishing",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -3497,9 +3524,10 @@
     <hyperlink ref="B14" r:id="rId7" xr:uid="{94F79A4B-2B5C-4EA8-BF54-F1A46823B28F}"/>
     <hyperlink ref="B15" r:id="rId8" xr:uid="{7CCF3CBC-9888-47D3-B716-3ED9479A9E74}"/>
     <hyperlink ref="B16" r:id="rId9" xr:uid="{817429EC-A709-424A-8419-A40EBE113331}"/>
+    <hyperlink ref="B17" r:id="rId10" xr:uid="{BBEFAC49-EB71-47D8-8596-1DF30DA66E2C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId10"/>
-  <drawing r:id="rId11"/>
+  <pageSetup fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId11"/>
+  <drawing r:id="rId12"/>
 </worksheet>
 </file>
--- a/test summary.xlsx
+++ b/test summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vansh\projects\ClueWell-Mail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEBAB14-AAD3-42DD-931D-F0198148B2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCFF0BF-BF85-48BE-9736-D97AAC9C33AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B026CC31-BFE6-4175-9DC2-82E30F74CC32}"/>
   </bookViews>
@@ -367,7 +367,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.499984740745262"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -539,14 +539,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -744,9 +744,29 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="4000" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>ClueWell</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="4000" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>-Mail</a:t>
+          </a:r>
           <a:r>
             <a:rPr lang="en-IN" sz="4000" b="1" baseline="0"/>
-            <a:t>ClueWell-Mail Testing Summary</a:t>
+            <a:t> Testing Summary</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1079,7 +1099,7 @@
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
     <col min="2" max="2" width="43" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="77" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="89.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.109375" customWidth="1"/>
     <col min="6" max="6" width="12.5546875" customWidth="1"/>
     <col min="7" max="7" width="13.44140625" customWidth="1"/>
@@ -1090,16 +1110,16 @@
   <sheetData>
     <row r="1" spans="1:9" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="25"/>
     </row>
     <row r="2" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
@@ -1555,7 +1575,7 @@
         <f t="shared" si="0"/>
         <v>Test 015</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="23" t="s">
         <v>58</v>
       </c>
       <c r="C17" s="9" t="s">

--- a/test summary.xlsx
+++ b/test summary.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="244">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -293,7 +293,10 @@
 Thank you for shopping with us.
 Customer Rewards Department
 Retail Promotions &amp; Member Benefits
-ChatGPT can make mistakes. Check important info.</t>
+</t>
+  </si>
+  <si>
+    <t>spam</t>
   </si>
   <si>
     <t>security-alert@onlinebank-support.com</t>
@@ -1973,7 +1976,7 @@
         <v>18</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="G17" s="13">
         <v>0.12</v>
@@ -1991,13 +1994,13 @@
         <v>Test 016</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>13</v>
@@ -2006,13 +2009,13 @@
         <v>13</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2021,13 +2024,13 @@
         <v>Test 017</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>13</v>
@@ -2036,10 +2039,10 @@
         <v>13</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>14</v>
@@ -2051,13 +2054,13 @@
         <v>Test 018</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>13</v>
@@ -2066,10 +2069,10 @@
         <v>13</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I20" s="14" t="s">
         <v>14</v>
@@ -2081,13 +2084,13 @@
         <v>Test 019</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>13</v>
@@ -2096,10 +2099,10 @@
         <v>13</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>14</v>
@@ -2111,25 +2114,25 @@
         <v>Test 020</v>
       </c>
       <c r="B22" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>77</v>
-      </c>
       <c r="H22" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I22" s="14" t="s">
         <v>14</v>
@@ -2141,13 +2144,13 @@
         <v>Test 021</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>13</v>
@@ -2156,10 +2159,10 @@
         <v>13</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>14</v>
@@ -2171,13 +2174,13 @@
         <v>Test 022</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>13</v>
@@ -2186,13 +2189,13 @@
         <v>22</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2201,28 +2204,28 @@
         <v>Test 023</v>
       </c>
       <c r="B25" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="I25" s="14" t="s">
         <v>90</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2231,13 +2234,13 @@
         <v>Test 024</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>13</v>
@@ -2246,13 +2249,13 @@
         <v>13</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2261,13 +2264,13 @@
         <v>Test 025</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>13</v>
@@ -2276,13 +2279,13 @@
         <v>13</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2291,13 +2294,13 @@
         <v>Test 026</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>13</v>
@@ -2306,13 +2309,13 @@
         <v>22</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2321,13 +2324,13 @@
         <v>Test 027</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>13</v>
@@ -2336,13 +2339,13 @@
         <v>22</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2351,28 +2354,28 @@
         <v>Test 028</v>
       </c>
       <c r="B30" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="I30" s="14" t="s">
         <v>113</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="I30" s="14" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2381,13 +2384,13 @@
         <v>Test 029</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E31" s="12" t="s">
         <v>13</v>
@@ -2396,10 +2399,10 @@
         <v>22</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I31" s="14" t="s">
         <v>41</v>
@@ -2411,13 +2414,13 @@
         <v>Test 030</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>13</v>
@@ -2426,10 +2429,10 @@
         <v>13</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I32" s="14" t="s">
         <v>14</v>
@@ -2441,13 +2444,13 @@
         <v>Test 031</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>13</v>
@@ -2456,13 +2459,13 @@
         <v>22</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2471,13 +2474,13 @@
         <v>Test 032</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>13</v>
@@ -2486,10 +2489,10 @@
         <v>22</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I34" s="14" t="s">
         <v>41</v>
@@ -2501,13 +2504,13 @@
         <v>Test 033</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E35" s="12" t="s">
         <v>13</v>
@@ -2516,10 +2519,10 @@
         <v>13</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I35" s="14" t="s">
         <v>14</v>
@@ -2531,13 +2534,13 @@
         <v>Test 034</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>13</v>
@@ -2546,10 +2549,10 @@
         <v>22</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I36" s="14" t="s">
         <v>41</v>
@@ -2561,13 +2564,13 @@
         <v>Test 035</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>13</v>
@@ -2576,10 +2579,10 @@
         <v>13</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I37" s="14" t="s">
         <v>14</v>
@@ -2591,13 +2594,13 @@
         <v>Test 036</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>13</v>
@@ -2606,10 +2609,10 @@
         <v>22</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I38" s="14" t="s">
         <v>41</v>
@@ -2621,13 +2624,13 @@
         <v>Test 037</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E39" s="12" t="s">
         <v>13</v>
@@ -2636,10 +2639,10 @@
         <v>13</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I39" s="14" t="s">
         <v>14</v>
@@ -2651,13 +2654,13 @@
         <v>Test 038</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>18</v>
@@ -2666,10 +2669,10 @@
         <v>22</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I40" s="14" t="s">
         <v>41</v>
@@ -2681,13 +2684,13 @@
         <v>Test 039</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E41" s="12" t="s">
         <v>18</v>
@@ -2696,10 +2699,10 @@
         <v>22</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I41" s="14" t="s">
         <v>41</v>
@@ -2711,13 +2714,13 @@
         <v>Test 040</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>18</v>
@@ -2726,10 +2729,10 @@
         <v>22</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I42" s="14" t="s">
         <v>41</v>
@@ -2741,13 +2744,13 @@
         <v>Test 041</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>18</v>
@@ -2756,10 +2759,10 @@
         <v>22</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I43" s="14" t="s">
         <v>41</v>
@@ -2771,13 +2774,13 @@
         <v>Test 042</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>13</v>
@@ -2786,10 +2789,10 @@
         <v>22</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I44" s="14" t="s">
         <v>41</v>
@@ -2801,13 +2804,13 @@
         <v>Test 043</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>13</v>
@@ -2816,10 +2819,10 @@
         <v>22</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I45" s="14" t="s">
         <v>41</v>
@@ -2831,28 +2834,28 @@
         <v>Test 044</v>
       </c>
       <c r="B46" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H46" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="E46" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="H46" s="12" t="s">
-        <v>175</v>
-      </c>
       <c r="I46" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2861,13 +2864,13 @@
         <v>Test 045</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>13</v>
@@ -2876,10 +2879,10 @@
         <v>22</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I47" s="14" t="s">
         <v>41</v>
@@ -2891,13 +2894,13 @@
         <v>Test 046</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>22</v>
@@ -2906,10 +2909,10 @@
         <v>22</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I48" s="14" t="s">
         <v>14</v>
@@ -2921,13 +2924,13 @@
         <v>Test 047</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E49" s="12" t="s">
         <v>22</v>
@@ -2936,10 +2939,10 @@
         <v>22</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I49" s="14" t="s">
         <v>14</v>
@@ -2951,13 +2954,13 @@
         <v>Test 048</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>22</v>
@@ -2966,10 +2969,10 @@
         <v>22</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I50" s="14" t="s">
         <v>14</v>
@@ -2981,13 +2984,13 @@
         <v>Test 049</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E51" s="12" t="s">
         <v>22</v>
@@ -2996,10 +2999,10 @@
         <v>22</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I51" s="14" t="s">
         <v>14</v>
@@ -3011,13 +3014,13 @@
         <v>Test 050</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>22</v>
@@ -3026,10 +3029,10 @@
         <v>22</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I52" s="14" t="s">
         <v>14</v>
@@ -3041,13 +3044,13 @@
         <v>Test 051</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>22</v>
@@ -3056,10 +3059,10 @@
         <v>22</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I53" s="14" t="s">
         <v>14</v>
@@ -3071,13 +3074,13 @@
         <v>Test 052</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>22</v>
@@ -3086,10 +3089,10 @@
         <v>22</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I54" s="14" t="s">
         <v>14</v>
@@ -3101,13 +3104,13 @@
         <v>Test 053</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E55" s="12" t="s">
         <v>22</v>
@@ -3116,10 +3119,10 @@
         <v>22</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I55" s="14" t="s">
         <v>14</v>
@@ -3131,13 +3134,13 @@
         <v>Test 054</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>22</v>
@@ -3146,10 +3149,10 @@
         <v>22</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I56" s="14" t="s">
         <v>14</v>
@@ -3161,13 +3164,13 @@
         <v>Test 055</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>22</v>
@@ -3176,10 +3179,10 @@
         <v>22</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I57" s="14" t="s">
         <v>14</v>
@@ -3191,13 +3194,13 @@
         <v>Test 056</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>18</v>
@@ -3206,10 +3209,10 @@
         <v>22</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I58" s="14" t="s">
         <v>41</v>
@@ -3221,13 +3224,13 @@
         <v>Test 057</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E59" s="12" t="s">
         <v>18</v>
@@ -3236,10 +3239,10 @@
         <v>18</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I59" s="14" t="s">
         <v>14</v>
@@ -3251,13 +3254,13 @@
         <v>Test 058</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>18</v>
@@ -3266,13 +3269,13 @@
         <v>22</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3281,13 +3284,13 @@
         <v>Test 059</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E61" s="12" t="s">
         <v>18</v>
@@ -3296,13 +3299,13 @@
         <v>22</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I61" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3311,13 +3314,13 @@
         <v>Test 060</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>18</v>
@@ -3326,10 +3329,10 @@
         <v>22</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I62" s="14" t="s">
         <v>41</v>
@@ -3341,13 +3344,13 @@
         <v>Test 061</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E63" s="12" t="s">
         <v>13</v>
@@ -3356,10 +3359,10 @@
         <v>22</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I63" s="14" t="s">
         <v>41</v>
@@ -3371,13 +3374,13 @@
         <v>Test 062</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E64" s="12" t="s">
         <v>13</v>
@@ -3386,10 +3389,10 @@
         <v>22</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I64" s="14" t="s">
         <v>41</v>
@@ -3401,13 +3404,13 @@
         <v>Test 063</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E65" s="12" t="s">
         <v>22</v>
@@ -3416,10 +3419,10 @@
         <v>22</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I65" s="14" t="s">
         <v>14</v>
@@ -3431,13 +3434,13 @@
         <v>Test 064</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>22</v>
@@ -3446,10 +3449,10 @@
         <v>22</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I66" s="14" t="s">
         <v>14</v>
@@ -3461,13 +3464,13 @@
         <v>Test 065</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E67" s="12" t="s">
         <v>13</v>
@@ -3476,13 +3479,13 @@
         <v>22</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I67" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
